--- a/data/processed/sam_auto_dashboard_2024_refresh/occ_change_by_education/segment_occ_change_by_education_2021_2024_auto.xlsx
+++ b/data/processed/sam_auto_dashboard_2024_refresh/occ_change_by_education/segment_occ_change_by_education_2021_2024_auto.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="34">
   <si>
     <t>methodology</t>
   </si>
@@ -46,6 +46,15 @@
   </si>
   <si>
     <t>pct_change</t>
+  </si>
+  <si>
+    <t>share_base</t>
+  </si>
+  <si>
+    <t>share_target</t>
+  </si>
+  <si>
+    <t>share_change</t>
   </si>
   <si>
     <t>sam_mi_moodys_mi</t>
@@ -90,16 +99,16 @@
     <t>BA+</t>
   </si>
   <si>
+    <t>SC or Associate's</t>
+  </si>
+  <si>
     <t>HS or Less</t>
   </si>
   <si>
-    <t>SC or Associate's</t>
+    <t>SC/Associate or Employer Training</t>
   </si>
   <si>
     <t>HS or Less - Limited Training</t>
-  </si>
-  <si>
-    <t>SC/Associate or Employer Training</t>
   </si>
   <si>
     <t>Associate's</t>
@@ -466,10 +475,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -500,601 +509,772 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>3611.463708453283</v>
+        <v>3611.463708887871</v>
       </c>
       <c r="H2">
         <v>3451.96904055808</v>
       </c>
       <c r="I2">
-        <v>-159.4946678952024</v>
+        <v>-159.4946683297908</v>
       </c>
       <c r="J2">
-        <v>-0.04416344196450772</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>-0.04416344207952908</v>
+      </c>
+      <c r="K2">
+        <v>0.1701849450208145</v>
+      </c>
+      <c r="L2">
+        <v>0.1624634248293149</v>
+      </c>
+      <c r="M2">
+        <v>-5.939990841276328</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>16702.03830175917</v>
+        <v>907.3157773431059</v>
       </c>
       <c r="H3">
-        <v>16795.04319647182</v>
+        <v>1000.656548635188</v>
       </c>
       <c r="I3">
-        <v>93.00489471265246</v>
+        <v>93.34077129208163</v>
       </c>
       <c r="J3">
-        <v>0.005568475717293533</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>0.1028757281895963</v>
+      </c>
+      <c r="K3">
+        <v>0.04275592893364671</v>
+      </c>
+      <c r="L3">
+        <v>0.04709488644280301</v>
+      </c>
+      <c r="M3">
+        <v>3.47624991103902</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>907.3157772339232</v>
+        <v>16702.03830376902</v>
       </c>
       <c r="H4">
-        <v>1000.656548635188</v>
+        <v>16795.04319647182</v>
       </c>
       <c r="I4">
-        <v>93.34077140126431</v>
+        <v>93.00489270280013</v>
       </c>
       <c r="J4">
-        <v>0.1028757283223119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>0.005568475596287695</v>
+      </c>
+      <c r="K4">
+        <v>0.787059126045539</v>
+      </c>
+      <c r="L4">
+        <v>0.7904416887278821</v>
+      </c>
+      <c r="M4">
+        <v>3.463740930237308</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>1521.561144388543</v>
+        <v>1521.56114435712</v>
       </c>
       <c r="H5">
         <v>1664.428681321303</v>
       </c>
       <c r="I5">
-        <v>142.8675369327595</v>
+        <v>142.8675369641824</v>
       </c>
       <c r="J5">
-        <v>0.0938953636267917</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>0.09389536364938249</v>
+      </c>
+      <c r="K5">
+        <v>0.2481144628268553</v>
+      </c>
+      <c r="L5">
+        <v>0.2665394402035619</v>
+      </c>
+      <c r="M5">
+        <v>1.274578082014771</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>3791.559111047778</v>
+        <v>819.3765246734049</v>
       </c>
       <c r="H6">
-        <v>3887.639306570689</v>
+        <v>692.5188546786338</v>
       </c>
       <c r="I6">
-        <v>96.08019552291171</v>
+        <v>-126.8576699947711</v>
       </c>
       <c r="J6">
-        <v>0.02534055060435559</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>-0.1548221924533843</v>
+      </c>
+      <c r="K6">
+        <v>0.1336122225690602</v>
+      </c>
+      <c r="L6">
+        <v>0.1108990670059372</v>
+      </c>
+      <c r="M6">
+        <v>-1.131747695428771</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G7">
-        <v>819.3765246903264</v>
+        <v>3791.559110969476</v>
       </c>
       <c r="H7">
-        <v>692.5188546786338</v>
+        <v>3887.639306570689</v>
       </c>
       <c r="I7">
-        <v>-126.8576700116926</v>
+        <v>96.08019560121329</v>
       </c>
       <c r="J7">
-        <v>-0.1548221924708386</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>0.02534055062553046</v>
+      </c>
+      <c r="K7">
+        <v>0.6182733146040845</v>
+      </c>
+      <c r="L7">
+        <v>0.6225614927905009</v>
+      </c>
+      <c r="M7">
+        <v>0.8571696134139996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G8">
-        <v>1135.537160196007</v>
+        <v>1135.537160232705</v>
       </c>
       <c r="H8">
         <v>1144.895853088782</v>
       </c>
       <c r="I8">
-        <v>9.35869289277457</v>
+        <v>9.358692856077141</v>
       </c>
       <c r="J8">
-        <v>0.00824164388522446</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>0.008241643852640871</v>
+      </c>
+      <c r="K8">
+        <v>0.128107433271053</v>
+      </c>
+      <c r="L8">
+        <v>0.1268844221105523</v>
+      </c>
+      <c r="M8">
+        <v>0.05878751773480197</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G9">
-        <v>7242.449489559899</v>
+        <v>485.9577069733402</v>
       </c>
       <c r="H9">
-        <v>7470.162051341688</v>
+        <v>408.0816902098634</v>
       </c>
       <c r="I9">
-        <v>227.7125617817892</v>
+        <v>-77.87601676347674</v>
       </c>
       <c r="J9">
-        <v>0.03144137382111402</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>-0.1602526632379329</v>
+      </c>
+      <c r="K9">
+        <v>0.05482409268392705</v>
+      </c>
+      <c r="L9">
+        <v>0.04522613065326623</v>
+      </c>
+      <c r="M9">
+        <v>-0.4891855932237134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G10">
-        <v>485.9577069576354</v>
+        <v>7242.449489793955</v>
       </c>
       <c r="H10">
-        <v>408.0816902098634</v>
+        <v>7470.162051341688</v>
       </c>
       <c r="I10">
-        <v>-77.87601674777198</v>
+        <v>227.7125615477335</v>
       </c>
       <c r="J10">
-        <v>-0.1602526632107946</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>0.03144137378778072</v>
+      </c>
+      <c r="K10">
+        <v>0.8170684740450198</v>
+      </c>
+      <c r="L10">
+        <v>0.8278894472361815</v>
+      </c>
+      <c r="M10">
+        <v>1.430398075488911</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G11">
-        <v>2401.9383520962</v>
+        <v>2401.938351846979</v>
       </c>
       <c r="H11">
         <v>2548.713461124355</v>
       </c>
       <c r="I11">
-        <v>146.7751090281545</v>
+        <v>146.7751092773751</v>
       </c>
       <c r="J11">
-        <v>0.06110694260744123</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>0.06110694271753971</v>
+      </c>
+      <c r="K11">
+        <v>0.168889161176508</v>
+      </c>
+      <c r="L11">
+        <v>0.1706372264187481</v>
+      </c>
+      <c r="M11">
+        <v>0.2054338696054571</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G12">
-        <v>11077.65602894763</v>
+        <v>742.3860903547931</v>
       </c>
       <c r="H12">
-        <v>11600.84106595768</v>
+        <v>786.889967566202</v>
       </c>
       <c r="I12">
-        <v>523.1850370100528</v>
+        <v>44.50387721140896</v>
       </c>
       <c r="J12">
-        <v>0.04722885740836234</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>0.05994707846713582</v>
+      </c>
+      <c r="K12">
+        <v>0.05219990928273246</v>
+      </c>
+      <c r="L12">
+        <v>0.05268254890567475</v>
+      </c>
+      <c r="M12">
+        <v>0.06228987839285611</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G13">
-        <v>742.3860904318217</v>
+        <v>11077.65602779823</v>
       </c>
       <c r="H13">
-        <v>786.889967566202</v>
+        <v>11600.84106595768</v>
       </c>
       <c r="I13">
-        <v>44.50387713438033</v>
+        <v>523.1850381594486</v>
       </c>
       <c r="J13">
-        <v>0.05994707835715764</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>0.04722885751702074</v>
+      </c>
+      <c r="K13">
+        <v>0.7789109295407595</v>
+      </c>
+      <c r="L13">
+        <v>0.7766802246755772</v>
+      </c>
+      <c r="M13">
+        <v>0.7322762520016868</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D14">
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G14">
-        <v>1871.485359674304</v>
+        <v>1871.485359584243</v>
       </c>
       <c r="H14">
         <v>2443.987754662811</v>
       </c>
       <c r="I14">
-        <v>572.5023949885076</v>
+        <v>572.502395078568</v>
       </c>
       <c r="J14">
-        <v>0.3059080275616693</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>0.3059080276245129</v>
+      </c>
+      <c r="K14">
+        <v>0.3380359538615803</v>
+      </c>
+      <c r="L14">
+        <v>0.4082140634723086</v>
+      </c>
+      <c r="M14">
+        <v>1.270322451337524</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D15">
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F15" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G15">
-        <v>3439.403934844128</v>
+        <v>225.4607247371421</v>
       </c>
       <c r="H15">
-        <v>3200.282745816092</v>
+        <v>342.7543802271001</v>
       </c>
       <c r="I15">
-        <v>-239.1211890280365</v>
+        <v>117.293655489958</v>
       </c>
       <c r="J15">
-        <v>-0.06952402031222114</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>0.5202398583021818</v>
+      </c>
+      <c r="K15">
+        <v>0.04072371218643899</v>
+      </c>
+      <c r="L15">
+        <v>0.05724953329184791</v>
+      </c>
+      <c r="M15">
+        <v>0.2602622543577204</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D16">
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F16" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G16">
-        <v>225.4607247479918</v>
+        <v>3439.403934678616</v>
       </c>
       <c r="H16">
-        <v>342.7543802271001</v>
+        <v>3200.282745816092</v>
       </c>
       <c r="I16">
-        <v>117.2936554791083</v>
+        <v>-239.1211888625239</v>
       </c>
       <c r="J16">
-        <v>0.5202398582290244</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>-0.06952402026744435</v>
+      </c>
+      <c r="K16">
+        <v>0.6212403339519807</v>
+      </c>
+      <c r="L16">
+        <v>0.5345364032358435</v>
+      </c>
+      <c r="M16">
+        <v>-0.530584705695244</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D17">
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G17">
-        <v>707.6201280068898</v>
+        <v>707.6201280218149</v>
       </c>
       <c r="H17">
         <v>737.9275791029602</v>
       </c>
       <c r="I17">
-        <v>30.30745109607039</v>
+        <v>30.30745108114525</v>
       </c>
       <c r="J17">
-        <v>0.04283011448732462</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>0.04283011446532922</v>
+      </c>
+      <c r="K17">
+        <v>0.7214470007469835</v>
+      </c>
+      <c r="L17">
+        <v>0.7150284321689701</v>
+      </c>
+      <c r="M17">
+        <v>0.5920467287400174</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D18">
         <v>6</v>
       </c>
       <c r="E18" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G18">
-        <v>169.4258159248505</v>
+        <v>103.7885834497608</v>
       </c>
       <c r="H18">
-        <v>199.9497019041748</v>
+        <v>94.14822441861125</v>
       </c>
       <c r="I18">
-        <v>30.52388597932426</v>
+        <v>-9.6403590311496</v>
       </c>
       <c r="J18">
-        <v>0.1801607730953071</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>-0.0928845804684871</v>
+      </c>
+      <c r="K18">
+        <v>0.1058166087656845</v>
+      </c>
+      <c r="L18">
+        <v>0.09122664500406108</v>
+      </c>
+      <c r="M18">
+        <v>-0.1883214465310862</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D19">
         <v>6</v>
       </c>
       <c r="E19" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F19" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G19">
-        <v>103.7885834475717</v>
+        <v>169.4258159284241</v>
       </c>
       <c r="H19">
-        <v>94.14822441861125</v>
+        <v>199.9497019041748</v>
       </c>
       <c r="I19">
-        <v>-9.640359028960475</v>
+        <v>30.52388597575072</v>
       </c>
       <c r="J19">
-        <v>-0.09288458044935408</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>0.180160773070415</v>
+      </c>
+      <c r="K19">
+        <v>0.172736390487332</v>
+      </c>
+      <c r="L19">
+        <v>0.1937449228269689</v>
+      </c>
+      <c r="M19">
+        <v>0.5962747177910688</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D20">
         <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F20" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G20">
         <v>25481.64392898052</v>
@@ -1108,185 +1288,239 @@
       <c r="J20">
         <v>0.1153416383645893</v>
       </c>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="K20">
+        <v>0.1457184745665642</v>
+      </c>
+      <c r="L20">
+        <v>0.1642038946162641</v>
+      </c>
+      <c r="M20">
+        <v>-1.644708762726214</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D21">
         <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F21" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G21">
-        <v>140934.9705612829</v>
+        <v>8452.385509736538</v>
       </c>
       <c r="H21">
-        <v>136344.2054982822</v>
+        <v>8317.056013745616</v>
       </c>
       <c r="I21">
-        <v>-4590.765063000756</v>
+        <v>-135.3294959909217</v>
       </c>
       <c r="J21">
-        <v>-0.03257364048623083</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>-0.01601080497748617</v>
+      </c>
+      <c r="K21">
+        <v>0.04833552836544235</v>
+      </c>
+      <c r="L21">
+        <v>0.04805269186712435</v>
+      </c>
+      <c r="M21">
+        <v>0.07572999216056163</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D22">
         <v>7</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F22" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G22">
-        <v>8452.385509736538</v>
+        <v>140934.9705612829</v>
       </c>
       <c r="H22">
-        <v>8317.056013745616</v>
+        <v>136344.2054982822</v>
       </c>
       <c r="I22">
-        <v>-135.3294959909217</v>
+        <v>-4590.765063000756</v>
       </c>
       <c r="J22">
-        <v>-0.01601080497748617</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>-0.03257364048623083</v>
+      </c>
+      <c r="K22">
+        <v>0.8059459970679934</v>
+      </c>
+      <c r="L22">
+        <v>0.7877434135166117</v>
+      </c>
+      <c r="M22">
+        <v>2.568978770565653</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D23">
         <v>8</v>
       </c>
       <c r="E23" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G23">
-        <v>16239.19907449228</v>
+        <v>16239.19907059248</v>
       </c>
       <c r="H23">
         <v>19646.96893063571</v>
       </c>
       <c r="I23">
-        <v>3407.76985614343</v>
+        <v>3407.769860043232</v>
       </c>
       <c r="J23">
-        <v>0.2098483946475035</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>0.2098483949380455</v>
+      </c>
+      <c r="K23">
+        <v>0.1538580630692243</v>
+      </c>
+      <c r="L23">
+        <v>0.1703395953757215</v>
+      </c>
+      <c r="M23">
+        <v>0.3479668013212717</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D24">
         <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G24">
-        <v>81069.25312920044</v>
+        <v>8238.171417630056</v>
       </c>
       <c r="H24">
-        <v>87775.90679190768</v>
+        <v>7917.124277456613</v>
       </c>
       <c r="I24">
-        <v>6706.653662707235</v>
+        <v>-321.047140173443</v>
       </c>
       <c r="J24">
-        <v>0.08272746329633517</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>-0.03897067976594755</v>
+      </c>
+      <c r="K24">
+        <v>0.07805243916518856</v>
+      </c>
+      <c r="L24">
+        <v>0.06864161849710952</v>
+      </c>
+      <c r="M24">
+        <v>-0.03278206892706002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D25">
         <v>8</v>
       </c>
       <c r="E25" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F25" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G25">
-        <v>8238.171419201557</v>
+        <v>81069.25311177746</v>
       </c>
       <c r="H25">
-        <v>7917.124277456613</v>
+        <v>87775.90679190768</v>
       </c>
       <c r="I25">
-        <v>-321.0471417449444</v>
+        <v>6706.653680130214</v>
       </c>
       <c r="J25">
-        <v>-0.03897067994927207</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>0.08272746352902928</v>
+      </c>
+      <c r="K25">
+        <v>0.7680894977655871</v>
+      </c>
+      <c r="L25">
+        <v>0.761018786127169</v>
+      </c>
+      <c r="M25">
+        <v>0.6848152676057883</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D26">
         <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F26" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G26">
         <v>4753.509400961959</v>
@@ -1300,89 +1534,116 @@
       <c r="J26">
         <v>0.2932428539207336</v>
       </c>
-    </row>
-    <row r="27" spans="1:10">
+      <c r="K26">
+        <v>0.07180744736943652</v>
+      </c>
+      <c r="L26">
+        <v>0.08832531700918218</v>
+      </c>
+      <c r="M26">
+        <v>0.4097391719215522</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D27">
         <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F27" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G27">
-        <v>44998.14808336977</v>
+        <v>16446.34251566827</v>
       </c>
       <c r="H27">
-        <v>45578.31219938782</v>
+        <v>17874.24573677311</v>
       </c>
       <c r="I27">
-        <v>580.1641160180443</v>
+        <v>1427.903221104836</v>
       </c>
       <c r="J27">
-        <v>0.0128930665089406</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>0.08682193136525562</v>
+      </c>
+      <c r="K27">
+        <v>0.248441682764861</v>
+      </c>
+      <c r="L27">
+        <v>0.2568138755283492</v>
+      </c>
+      <c r="M27">
+        <v>0.4197246387727323</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D28">
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F28" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G28">
-        <v>16446.34251566827</v>
+        <v>44998.14808336977</v>
       </c>
       <c r="H28">
-        <v>17874.24573677311</v>
+        <v>45578.31219938782</v>
       </c>
       <c r="I28">
-        <v>1427.903221104836</v>
+        <v>580.1641160180443</v>
       </c>
       <c r="J28">
-        <v>0.08682193136525562</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>0.0128930665089406</v>
+      </c>
+      <c r="K28">
+        <v>0.6797508698657024</v>
+      </c>
+      <c r="L28">
+        <v>0.6548608074624687</v>
+      </c>
+      <c r="M28">
+        <v>0.1705361893057155</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D29">
         <v>10</v>
       </c>
       <c r="E29" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F29" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G29">
         <v>1791.908006814309</v>
@@ -1396,69 +1657,96 @@
       <c r="J29">
         <v>1.184304796311249</v>
       </c>
-    </row>
-    <row r="30" spans="1:10">
+      <c r="K29">
+        <v>0.03831319236293157</v>
+      </c>
+      <c r="L29">
+        <v>0.08347529812606426</v>
+      </c>
+      <c r="M29">
+        <v>17.83332140351816</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D30">
         <v>10</v>
       </c>
       <c r="E30" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F30" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G30">
-        <v>14932.33816013629</v>
+        <v>30045.75383304941</v>
       </c>
       <c r="H30">
-        <v>15786.09646507664</v>
+        <v>27188.83028109034</v>
       </c>
       <c r="I30">
-        <v>853.7583049403511</v>
+        <v>-2856.923551959066</v>
       </c>
       <c r="J30">
-        <v>0.05717512527405547</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>-0.0950857671214938</v>
+      </c>
+      <c r="K30">
+        <v>0.6424150915768528</v>
+      </c>
+      <c r="L30">
+        <v>0.5798551959114151</v>
+      </c>
+      <c r="M30">
+        <v>-24.00776094083184</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D31">
         <v>10</v>
       </c>
       <c r="E31" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F31" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G31">
-        <v>30045.75383304941</v>
+        <v>14932.33816013629</v>
       </c>
       <c r="H31">
-        <v>27188.83028109034</v>
+        <v>15786.09646507664</v>
       </c>
       <c r="I31">
-        <v>-2856.923551959066</v>
+        <v>853.7583049403511</v>
       </c>
       <c r="J31">
-        <v>-0.0950857671214938</v>
+        <v>0.05717512527405547</v>
+      </c>
+      <c r="K31">
+        <v>0.3192717160602156</v>
+      </c>
+      <c r="L31">
+        <v>0.3366695059625208</v>
+      </c>
+      <c r="M31">
+        <v>7.174439537313683</v>
       </c>
     </row>
   </sheetData>
@@ -1468,10 +1756,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1502,601 +1790,772 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>3611.463708453283</v>
+        <v>3611.463708887871</v>
       </c>
       <c r="H2">
         <v>3451.96904055808</v>
       </c>
       <c r="I2">
-        <v>-159.4946678952024</v>
+        <v>-159.4946683297908</v>
       </c>
       <c r="J2">
-        <v>-0.04416344196450772</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>-0.04416344207952908</v>
+      </c>
+      <c r="K2">
+        <v>0.1701849450208144</v>
+      </c>
+      <c r="L2">
+        <v>0.1624634248293149</v>
+      </c>
+      <c r="M2">
+        <v>-5.939990841276529</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>4467.787947547226</v>
+        <v>13141.56613302727</v>
       </c>
       <c r="H3">
-        <v>4414.138798861176</v>
+        <v>13381.56094624583</v>
       </c>
       <c r="I3">
-        <v>-53.64914868605047</v>
+        <v>239.9948132185673</v>
       </c>
       <c r="J3">
-        <v>-0.01200798903526819</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>0.01826226880336693</v>
+      </c>
+      <c r="K3">
+        <v>0.6192770826777485</v>
+      </c>
+      <c r="L3">
+        <v>0.6297896056848274</v>
+      </c>
+      <c r="M3">
+        <v>8.938022865595002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>13141.56613144586</v>
+        <v>4467.787948084862</v>
       </c>
       <c r="H4">
-        <v>13381.56094624583</v>
+        <v>4414.138798861176</v>
       </c>
       <c r="I4">
-        <v>239.9948147999694</v>
+        <v>-53.64914922368644</v>
       </c>
       <c r="J4">
-        <v>0.01826226892590043</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>-0.01200798915415925</v>
+      </c>
+      <c r="K4">
+        <v>0.210537972301437</v>
+      </c>
+      <c r="L4">
+        <v>0.2077469694858577</v>
+      </c>
+      <c r="M4">
+        <v>-1.998032024318472</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>1521.561144388543</v>
+        <v>1521.56114435712</v>
       </c>
       <c r="H5">
         <v>1664.428681321303</v>
       </c>
       <c r="I5">
-        <v>142.8675369327595</v>
+        <v>142.8675369641824</v>
       </c>
       <c r="J5">
-        <v>0.0938953636267917</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>0.09389536364938249</v>
+      </c>
+      <c r="K5">
+        <v>0.2481144628268553</v>
+      </c>
+      <c r="L5">
+        <v>0.2665394402035619</v>
+      </c>
+      <c r="M5">
+        <v>1.274578082014772</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G6">
-        <v>858.7692085075396</v>
+        <v>3752.166427153076</v>
       </c>
       <c r="H6">
-        <v>855.3865776718878</v>
+        <v>3724.771583577435</v>
       </c>
       <c r="I6">
-        <v>-3.382630835651753</v>
+        <v>-27.39484357564106</v>
       </c>
       <c r="J6">
-        <v>-0.003938928878843302</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>-0.007301073688361596</v>
+      </c>
+      <c r="K6">
+        <v>0.6118497182729993</v>
+      </c>
+      <c r="L6">
+        <v>0.5964800678541141</v>
+      </c>
+      <c r="M6">
+        <v>-0.2444002880128684</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>3752.166427230564</v>
+        <v>858.7692084898047</v>
       </c>
       <c r="H7">
-        <v>3724.771583577435</v>
+        <v>855.3865776718878</v>
       </c>
       <c r="I7">
-        <v>-27.3948436531291</v>
+        <v>-3.382630817916834</v>
       </c>
       <c r="J7">
-        <v>-0.007301073708862364</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>-0.003938928858273093</v>
+      </c>
+      <c r="K7">
+        <v>0.1400358189001454</v>
+      </c>
+      <c r="L7">
+        <v>0.136980491942324</v>
+      </c>
+      <c r="M7">
+        <v>-0.03017779400190399</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G8">
-        <v>1135.537160196007</v>
+        <v>1135.537160232705</v>
       </c>
       <c r="H8">
         <v>1144.895853088782</v>
       </c>
       <c r="I8">
-        <v>9.35869289277457</v>
+        <v>9.358692856077141</v>
       </c>
       <c r="J8">
-        <v>0.00824164388522446</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>0.008241643852640871</v>
+      </c>
+      <c r="K8">
+        <v>0.128107433271053</v>
+      </c>
+      <c r="L8">
+        <v>0.1268844221105523</v>
+      </c>
+      <c r="M8">
+        <v>0.05878751773480185</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G9">
-        <v>1495.387658451127</v>
+        <v>6233.019538267842</v>
       </c>
       <c r="H9">
-        <v>1592.652152069054</v>
+        <v>6285.591589482498</v>
       </c>
       <c r="I9">
-        <v>97.26449361792743</v>
+        <v>52.57205121465631</v>
       </c>
       <c r="J9">
-        <v>0.06504299608749667</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>0.008434443513595355</v>
+      </c>
+      <c r="K9">
+        <v>0.7031880263717502</v>
+      </c>
+      <c r="L9">
+        <v>0.6966080402010055</v>
+      </c>
+      <c r="M9">
+        <v>0.3302363311484922</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G10">
-        <v>6233.019538066408</v>
+        <v>1495.387658499453</v>
       </c>
       <c r="H10">
-        <v>6285.591589482498</v>
+        <v>1592.652152069054</v>
       </c>
       <c r="I10">
-        <v>52.57205141609029</v>
+        <v>97.26449356960075</v>
       </c>
       <c r="J10">
-        <v>0.00843444354618517</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>0.06504299605307751</v>
+      </c>
+      <c r="K10">
+        <v>0.1687045403571968</v>
+      </c>
+      <c r="L10">
+        <v>0.1765075376884422</v>
+      </c>
+      <c r="M10">
+        <v>0.610976151116706</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G11">
-        <v>2401.9383520962</v>
+        <v>2401.938351846979</v>
       </c>
       <c r="H11">
         <v>2548.713461124355</v>
       </c>
       <c r="I11">
-        <v>146.7751090281545</v>
+        <v>146.7751092773751</v>
       </c>
       <c r="J11">
-        <v>0.06110694260744123</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>0.06110694271753971</v>
+      </c>
+      <c r="K11">
+        <v>0.168889161176508</v>
+      </c>
+      <c r="L11">
+        <v>0.1706372264187481</v>
+      </c>
+      <c r="M11">
+        <v>0.2054338696054571</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G12">
-        <v>2449.745427257848</v>
+        <v>9370.296691149357</v>
       </c>
       <c r="H12">
-        <v>2369.348836164419</v>
+        <v>10018.38219735946</v>
       </c>
       <c r="I12">
-        <v>-80.39659109342892</v>
+        <v>648.0855062101055</v>
       </c>
       <c r="J12">
-        <v>-0.03281834520390219</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>0.0691638192013973</v>
+      </c>
+      <c r="K12">
+        <v>0.6588601855357037</v>
+      </c>
+      <c r="L12">
+        <v>0.6707340693395321</v>
+      </c>
+      <c r="M12">
+        <v>0.9070932669131818</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G13">
-        <v>9370.296692121601</v>
+        <v>2449.745427003667</v>
       </c>
       <c r="H13">
-        <v>10018.38219735946</v>
+        <v>2369.348836164419</v>
       </c>
       <c r="I13">
-        <v>648.0855052378611</v>
+        <v>-80.39659083924789</v>
       </c>
       <c r="J13">
-        <v>0.06916381909046287</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>-0.03281834510354922</v>
+      </c>
+      <c r="K13">
+        <v>0.1722506532877883</v>
+      </c>
+      <c r="L13">
+        <v>0.1586287042417198</v>
+      </c>
+      <c r="M13">
+        <v>-0.1125271365186389</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D14">
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G14">
-        <v>1871.485359674304</v>
+        <v>1871.485359584243</v>
       </c>
       <c r="H14">
         <v>2443.987754662811</v>
       </c>
       <c r="I14">
-        <v>572.5023949885076</v>
+        <v>572.502395078568</v>
       </c>
       <c r="J14">
-        <v>0.3059080275616693</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>0.3059080276245129</v>
+      </c>
+      <c r="K14">
+        <v>0.3380359538615803</v>
+      </c>
+      <c r="L14">
+        <v>0.4082140634723086</v>
+      </c>
+      <c r="M14">
+        <v>1.270322451337524</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D15">
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G15">
-        <v>843.1753262865917</v>
+        <v>2821.689333169742</v>
       </c>
       <c r="H15">
-        <v>771.1973555109769</v>
+        <v>2771.839770532215</v>
       </c>
       <c r="I15">
-        <v>-71.97797077561484</v>
+        <v>-49.84956263752701</v>
       </c>
       <c r="J15">
-        <v>-0.08536536652775562</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>-0.01766656663847843</v>
+      </c>
+      <c r="K15">
+        <v>0.5096659935672577</v>
+      </c>
+      <c r="L15">
+        <v>0.4629744866210333</v>
+      </c>
+      <c r="M15">
+        <v>-0.1106109234689163</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D16">
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F16" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G16">
-        <v>2821.689333305529</v>
+        <v>843.175326246016</v>
       </c>
       <c r="H16">
-        <v>2771.839770532215</v>
+        <v>771.1973555109769</v>
       </c>
       <c r="I16">
-        <v>-49.84956277331366</v>
+        <v>-71.97797073503909</v>
       </c>
       <c r="J16">
-        <v>-0.01766656668575074</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>-0.08536536648374107</v>
+      </c>
+      <c r="K16">
+        <v>0.152298052571162</v>
+      </c>
+      <c r="L16">
+        <v>0.1288114499066581</v>
+      </c>
+      <c r="M16">
+        <v>-0.1597115278686078</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D17">
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G17">
-        <v>707.6201280068898</v>
+        <v>707.6201280218149</v>
       </c>
       <c r="H17">
         <v>737.9275791029602</v>
       </c>
       <c r="I17">
-        <v>30.30745109607039</v>
+        <v>30.30745108114525</v>
       </c>
       <c r="J17">
-        <v>0.04283011448732462</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>0.04283011446532922</v>
+      </c>
+      <c r="K17">
+        <v>0.7214470007469835</v>
+      </c>
+      <c r="L17">
+        <v>0.7150284321689699</v>
+      </c>
+      <c r="M17">
+        <v>0.5920467287400172</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D18">
         <v>6</v>
       </c>
       <c r="E18" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G18">
-        <v>61.65459154394989</v>
+        <v>211.5598078329346</v>
       </c>
       <c r="H18">
-        <v>76.96177205368217</v>
+        <v>217.1361542691039</v>
       </c>
       <c r="I18">
-        <v>15.30718050973228</v>
+        <v>5.576346436169274</v>
       </c>
       <c r="J18">
-        <v>0.2482731638700534</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>0.02635825062089688</v>
+      </c>
+      <c r="K18">
+        <v>0.2156936791302996</v>
+      </c>
+      <c r="L18">
+        <v>0.2103980503655553</v>
+      </c>
+      <c r="M18">
+        <v>0.1089322113237349</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D19">
         <v>6</v>
       </c>
       <c r="E19" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F19" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G19">
-        <v>211.5598078284724</v>
+        <v>61.65459154525031</v>
       </c>
       <c r="H19">
-        <v>217.1361542691039</v>
+        <v>76.96177205368217</v>
       </c>
       <c r="I19">
-        <v>5.576346440631511</v>
+        <v>15.30718050843186</v>
       </c>
       <c r="J19">
-        <v>0.02635825064254492</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>0.2482731638437247</v>
+      </c>
+      <c r="K19">
+        <v>0.06285932012271687</v>
+      </c>
+      <c r="L19">
+        <v>0.07457351746547462</v>
+      </c>
+      <c r="M19">
+        <v>0.2990210599362479</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D20">
         <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F20" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G20">
         <v>25481.64392898052</v>
@@ -2110,185 +2569,239 @@
       <c r="J20">
         <v>0.1153416383645893</v>
       </c>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="K20">
+        <v>0.1457184745665642</v>
+      </c>
+      <c r="L20">
+        <v>0.1642038946162641</v>
+      </c>
+      <c r="M20">
+        <v>-1.644708762726197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D21">
         <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F21" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G21">
-        <v>19056.2129438717</v>
+        <v>130331.1431271478</v>
       </c>
       <c r="H21">
-        <v>19251.15945017174</v>
+        <v>125410.102061856</v>
       </c>
       <c r="I21">
-        <v>194.9465063000389</v>
+        <v>-4921.041065291734</v>
       </c>
       <c r="J21">
-        <v>0.01023007597964169</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>-0.03775798283677211</v>
+      </c>
+      <c r="K21">
+        <v>0.7453073050520549</v>
+      </c>
+      <c r="L21">
+        <v>0.7245704467353974</v>
+      </c>
+      <c r="M21">
+        <v>2.753800260375912</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D22">
         <v>7</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F22" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G22">
-        <v>130331.1431271478</v>
+        <v>19056.2129438717</v>
       </c>
       <c r="H22">
-        <v>125410.102061856</v>
+        <v>19251.15945017174</v>
       </c>
       <c r="I22">
-        <v>-4921.041065291734</v>
+        <v>194.9465063000389</v>
       </c>
       <c r="J22">
-        <v>-0.03775798283677211</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>0.01023007597964169</v>
+      </c>
+      <c r="K22">
+        <v>0.1089742203813809</v>
+      </c>
+      <c r="L22">
+        <v>0.1112256586483386</v>
+      </c>
+      <c r="M22">
+        <v>-0.1090914976497144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D23">
         <v>8</v>
       </c>
       <c r="E23" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G23">
-        <v>16239.19907449228</v>
+        <v>16239.19907059248</v>
       </c>
       <c r="H23">
         <v>19646.96893063571</v>
       </c>
       <c r="I23">
-        <v>3407.76985614343</v>
+        <v>3407.769860043232</v>
       </c>
       <c r="J23">
-        <v>0.2098483946475035</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>0.2098483949380455</v>
+      </c>
+      <c r="K23">
+        <v>0.1538580630692243</v>
+      </c>
+      <c r="L23">
+        <v>0.1703395953757214</v>
+      </c>
+      <c r="M23">
+        <v>0.3479668013212716</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D24">
         <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G24">
-        <v>53645.91060476566</v>
+        <v>35661.5139367052</v>
       </c>
       <c r="H24">
-        <v>60774.34609826608</v>
+        <v>34918.68497109821</v>
       </c>
       <c r="I24">
-        <v>7128.435493500423</v>
+        <v>-742.8289656069901</v>
       </c>
       <c r="J24">
-        <v>0.1328793828483762</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>-0.02082998963323374</v>
+      </c>
+      <c r="K24">
+        <v>0.337874511948909</v>
+      </c>
+      <c r="L24">
+        <v>0.3027456647398839</v>
+      </c>
+      <c r="M24">
+        <v>-0.07585013944802424</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D25">
         <v>8</v>
       </c>
       <c r="E25" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F25" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G25">
-        <v>35661.51394363635</v>
+        <v>53645.91059270232</v>
       </c>
       <c r="H25">
-        <v>34918.68497109821</v>
+        <v>60774.34609826608</v>
       </c>
       <c r="I25">
-        <v>-742.8289725381328</v>
+        <v>7128.435505563764</v>
       </c>
       <c r="J25">
-        <v>-0.02082998982354443</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>0.1328793831031265</v>
+      </c>
+      <c r="K25">
+        <v>0.5082674249818666</v>
+      </c>
+      <c r="L25">
+        <v>0.5269147398843946</v>
+      </c>
+      <c r="M25">
+        <v>0.7278833381267527</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D26">
         <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F26" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G26">
         <v>4753.509400961959</v>
@@ -2302,89 +2815,116 @@
       <c r="J26">
         <v>0.2932428539207336</v>
       </c>
-    </row>
-    <row r="27" spans="1:10">
+      <c r="K26">
+        <v>0.07180744736943652</v>
+      </c>
+      <c r="L26">
+        <v>0.08832531700918218</v>
+      </c>
+      <c r="M26">
+        <v>0.4097391719215522</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D27">
         <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F27" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G27">
-        <v>35267.35344701938</v>
+        <v>26177.13715201865</v>
       </c>
       <c r="H27">
-        <v>34734.06209007435</v>
+        <v>28718.49584608657</v>
       </c>
       <c r="I27">
-        <v>-533.291356945032</v>
+        <v>2541.358694067912</v>
       </c>
       <c r="J27">
-        <v>-0.01512138861642035</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>0.09708314088395015</v>
+      </c>
+      <c r="K27">
+        <v>0.3954369792443677</v>
+      </c>
+      <c r="L27">
+        <v>0.4126220667541173</v>
+      </c>
+      <c r="M27">
+        <v>0.7470190164808674</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D28">
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F28" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G28">
-        <v>26177.13715201865</v>
+        <v>35267.35344701938</v>
       </c>
       <c r="H28">
-        <v>28718.49584608657</v>
+        <v>34734.06209007435</v>
       </c>
       <c r="I28">
-        <v>2541.358694067912</v>
+        <v>-533.291356945032</v>
       </c>
       <c r="J28">
-        <v>0.09708314088395015</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>-0.01512138861642035</v>
+      </c>
+      <c r="K28">
+        <v>0.5327555733861957</v>
+      </c>
+      <c r="L28">
+        <v>0.4990526162367004</v>
+      </c>
+      <c r="M28">
+        <v>-0.1567581884024197</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D29">
         <v>10</v>
       </c>
       <c r="E29" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F29" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G29">
         <v>1791.908006814309</v>
@@ -2398,69 +2938,96 @@
       <c r="J29">
         <v>1.184304796311249</v>
       </c>
-    </row>
-    <row r="30" spans="1:10">
+      <c r="K29">
+        <v>0.03831319236293157</v>
+      </c>
+      <c r="L29">
+        <v>0.08347529812606426</v>
+      </c>
+      <c r="M29">
+        <v>17.83332140351762</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D30">
         <v>10</v>
       </c>
       <c r="E30" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F30" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G30">
-        <v>10265.90289608177</v>
+        <v>34712.18909710392</v>
       </c>
       <c r="H30">
-        <v>10643.88287904598</v>
+        <v>32331.043867121</v>
       </c>
       <c r="I30">
-        <v>377.9799829642106</v>
+        <v>-2381.145229982922</v>
       </c>
       <c r="J30">
-        <v>0.03681897118941928</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>-0.06859680394462887</v>
+      </c>
+      <c r="K30">
+        <v>0.7421892045564233</v>
+      </c>
+      <c r="L30">
+        <v>0.6895229982964234</v>
+      </c>
+      <c r="M30">
+        <v>-20.00962378136794</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D31">
         <v>10</v>
       </c>
       <c r="E31" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F31" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G31">
-        <v>34712.18909710392</v>
+        <v>10265.90289608177</v>
       </c>
       <c r="H31">
-        <v>32331.043867121</v>
+        <v>10643.88287904598</v>
       </c>
       <c r="I31">
-        <v>-2381.145229982922</v>
+        <v>377.9799829642106</v>
       </c>
       <c r="J31">
-        <v>-0.06859680394462887</v>
+        <v>0.03681897118941928</v>
+      </c>
+      <c r="K31">
+        <v>0.2194976030806451</v>
+      </c>
+      <c r="L31">
+        <v>0.2270017035775125</v>
+      </c>
+      <c r="M31">
+        <v>3.176302377850328</v>
       </c>
     </row>
   </sheetData>
@@ -2470,10 +3037,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2504,857 +3071,1100 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>280.8009122285574</v>
+        <v>3611.463708887871</v>
       </c>
       <c r="H2">
-        <v>358.2232023220635</v>
+        <v>3451.96904055808</v>
       </c>
       <c r="I2">
-        <v>77.42229009350615</v>
+        <v>-159.4946683297908</v>
       </c>
       <c r="J2">
-        <v>0.2757195105922178</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>-0.04416344207952908</v>
+      </c>
+      <c r="K2">
+        <v>0.1701849450208144</v>
+      </c>
+      <c r="L2">
+        <v>0.1624634248293149</v>
+      </c>
+      <c r="M2">
+        <v>-5.939990841276793</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>3611.463708453283</v>
+        <v>280.8009122623478</v>
       </c>
       <c r="H3">
-        <v>3451.96904055808</v>
+        <v>358.2232023220635</v>
       </c>
       <c r="I3">
-        <v>-159.4946678952024</v>
+        <v>77.42229005971575</v>
       </c>
       <c r="J3">
-        <v>-0.04416344196450772</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>0.2757195104387031</v>
+      </c>
+      <c r="K3">
+        <v>0.01323233228055288</v>
+      </c>
+      <c r="L3">
+        <v>0.01685941201058921</v>
+      </c>
+      <c r="M3">
+        <v>2.88340481021263</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>12678.39143374983</v>
+        <v>12678.39143527549</v>
       </c>
       <c r="H4">
         <v>12813.14065826372</v>
       </c>
       <c r="I4">
-        <v>134.7492245138874</v>
+        <v>134.7492229882228</v>
       </c>
       <c r="J4">
-        <v>0.01062825873597698</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>0.0106282586143622</v>
+      </c>
+      <c r="K4">
+        <v>0.5974506525026572</v>
+      </c>
+      <c r="L4">
+        <v>0.6030374808415785</v>
+      </c>
+      <c r="M4">
+        <v>5.018406939874524</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>4650.161733014706</v>
+        <v>4650.161733574288</v>
       </c>
       <c r="H5">
         <v>4624.335884521229</v>
       </c>
       <c r="I5">
-        <v>-25.82584849347768</v>
+        <v>-25.82584905305885</v>
       </c>
       <c r="J5">
-        <v>-0.005553752745871646</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>-0.005553752865539181</v>
+      </c>
+      <c r="K5">
+        <v>0.2191320701959756</v>
+      </c>
+      <c r="L5">
+        <v>0.2176396823185174</v>
+      </c>
+      <c r="M5">
+        <v>-0.9618209088103611</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G6">
-        <v>90.07287735502943</v>
+        <v>1521.56114435712</v>
       </c>
       <c r="H6">
-        <v>109.9026098247154</v>
+        <v>1664.428681321303</v>
       </c>
       <c r="I6">
-        <v>19.82973246968598</v>
+        <v>142.8675369641824</v>
       </c>
       <c r="J6">
-        <v>0.2201520929716224</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>0.09389536364938249</v>
+      </c>
+      <c r="K6">
+        <v>0.2481144628268553</v>
+      </c>
+      <c r="L6">
+        <v>0.2665394402035619</v>
+      </c>
+      <c r="M6">
+        <v>1.274578082014766</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>1521.561144388543</v>
+        <v>90.07287735316929</v>
       </c>
       <c r="H7">
-        <v>1664.428681321303</v>
+        <v>109.9026098247154</v>
       </c>
       <c r="I7">
-        <v>142.8675369327595</v>
+        <v>19.82973247154612</v>
       </c>
       <c r="J7">
-        <v>0.0938953636267917</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>0.2201520929968204</v>
+      </c>
+      <c r="K7">
+        <v>0.01468779855652354</v>
+      </c>
+      <c r="L7">
+        <v>0.01759966072943158</v>
+      </c>
+      <c r="M7">
+        <v>0.176908924991026</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G8">
-        <v>3608.657947112561</v>
+        <v>3608.657947038036</v>
       </c>
       <c r="H8">
         <v>3583.089905851598</v>
       </c>
       <c r="I8">
-        <v>-25.56804126096313</v>
+        <v>-25.56804118643822</v>
       </c>
       <c r="J8">
-        <v>-0.007085193896368369</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>-0.007085193875862995</v>
+      </c>
+      <c r="K8">
+        <v>0.5884484047031224</v>
+      </c>
+      <c r="L8">
+        <v>0.5737913486005096</v>
+      </c>
+      <c r="M8">
+        <v>-0.2281026578099058</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G9">
-        <v>912.2048112705136</v>
+        <v>912.2048112516752</v>
       </c>
       <c r="H9">
         <v>887.16564557301</v>
       </c>
       <c r="I9">
-        <v>-25.03916569750356</v>
+        <v>-25.0391656786652</v>
       </c>
       <c r="J9">
-        <v>-0.02744906120658272</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>-0.02744906118649812</v>
+      </c>
+      <c r="K9">
+        <v>0.1487493339134986</v>
+      </c>
+      <c r="L9">
+        <v>0.1420695504664969</v>
+      </c>
+      <c r="M9">
+        <v>-0.2233843491958858</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G10">
-        <v>36.30569953101116</v>
+        <v>1135.537160232705</v>
       </c>
       <c r="H10">
-        <v>68.01361503497709</v>
+        <v>1144.895853088782</v>
       </c>
       <c r="I10">
-        <v>31.70791550396594</v>
+        <v>9.358692856077141</v>
       </c>
       <c r="J10">
-        <v>0.8733591671159526</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>0.008241643852640871</v>
+      </c>
+      <c r="K10">
+        <v>0.128107433271053</v>
+      </c>
+      <c r="L10">
+        <v>0.1268844221105523</v>
+      </c>
+      <c r="M10">
+        <v>0.05878751773480189</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G11">
-        <v>1135.537160196007</v>
+        <v>36.30569953218447</v>
       </c>
       <c r="H11">
-        <v>1144.895853088782</v>
+        <v>68.01361503497709</v>
       </c>
       <c r="I11">
-        <v>9.35869289277457</v>
+        <v>31.70791550279262</v>
       </c>
       <c r="J11">
-        <v>0.00824164388522446</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>0.8733591670554102</v>
+      </c>
+      <c r="K11">
+        <v>0.004095885315831577</v>
+      </c>
+      <c r="L11">
+        <v>0.007537688442211023</v>
+      </c>
+      <c r="M11">
+        <v>0.1991762817329344</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G12">
-        <v>6142.993584412438</v>
+        <v>6142.993584610963</v>
       </c>
       <c r="H12">
         <v>6183.571166930033</v>
       </c>
       <c r="I12">
-        <v>40.57758251759424</v>
+        <v>40.57758231906973</v>
       </c>
       <c r="J12">
-        <v>0.006605506250333384</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>0.006605506217802687</v>
+      </c>
+      <c r="K12">
+        <v>0.6930316050280416</v>
+      </c>
+      <c r="L12">
+        <v>0.685301507537689</v>
+      </c>
+      <c r="M12">
+        <v>0.2548919359682459</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G13">
-        <v>1549.107912574085</v>
+        <v>1549.107912624148</v>
       </c>
       <c r="H13">
         <v>1626.658959586543</v>
       </c>
       <c r="I13">
-        <v>77.5510470124575</v>
+        <v>77.55104696239459</v>
       </c>
       <c r="J13">
-        <v>0.05006174610753508</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>0.05006174607359998</v>
+      </c>
+      <c r="K13">
+        <v>0.1747650763850737</v>
+      </c>
+      <c r="L13">
+        <v>0.1802763819095477</v>
+      </c>
+      <c r="M13">
+        <v>0.4871442645640178</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D14">
         <v>4</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G14">
-        <v>180.2079374969467</v>
+        <v>2401.938351846979</v>
       </c>
       <c r="H14">
-        <v>257.4750261521749</v>
+        <v>2548.713461124355</v>
       </c>
       <c r="I14">
-        <v>77.26708865522818</v>
+        <v>146.7751092773751</v>
       </c>
       <c r="J14">
-        <v>0.4287662892570274</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>0.06110694271753971</v>
+      </c>
+      <c r="K14">
+        <v>0.168889161176508</v>
+      </c>
+      <c r="L14">
+        <v>0.1706372264187481</v>
+      </c>
+      <c r="M14">
+        <v>0.2054338696054571</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D15">
         <v>4</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G15">
-        <v>2401.9383520962</v>
+        <v>180.2079374782487</v>
       </c>
       <c r="H15">
-        <v>2548.713461124355</v>
+        <v>257.4750261521749</v>
       </c>
       <c r="I15">
-        <v>146.7751090281545</v>
+        <v>77.26708867392622</v>
       </c>
       <c r="J15">
-        <v>0.06110694260744123</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>0.4287662894052736</v>
+      </c>
+      <c r="K15">
+        <v>0.01267108598963282</v>
+      </c>
+      <c r="L15">
+        <v>0.01723803989928318</v>
+      </c>
+      <c r="M15">
+        <v>0.1081469269386499</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D16">
         <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G16">
-        <v>9109.059896505431</v>
+        <v>9109.059895560293</v>
       </c>
       <c r="H16">
         <v>9677.010814371186</v>
       </c>
       <c r="I16">
-        <v>567.9509178657554</v>
+        <v>567.9509188108932</v>
       </c>
       <c r="J16">
-        <v>0.06235011343856046</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>0.06235011354878778</v>
+      </c>
+      <c r="K16">
+        <v>0.6404916611139384</v>
+      </c>
+      <c r="L16">
+        <v>0.6478791400348646</v>
+      </c>
+      <c r="M16">
+        <v>0.7949328436663057</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D17">
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G17">
-        <v>2530.774285377072</v>
+        <v>2530.774285114484</v>
       </c>
       <c r="H17">
         <v>2453.245193000522</v>
       </c>
       <c r="I17">
-        <v>-77.52909237655058</v>
+        <v>-77.52909211396172</v>
       </c>
       <c r="J17">
-        <v>-0.0306345345867141</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>-0.03063453448613438</v>
+      </c>
+      <c r="K17">
+        <v>0.1779480917199208</v>
+      </c>
+      <c r="L17">
+        <v>0.1642455936471043</v>
+      </c>
+      <c r="M17">
+        <v>-0.1085136402104126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D18">
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G18">
-        <v>77.36726862332053</v>
+        <v>1871.485359584243</v>
       </c>
       <c r="H18">
-        <v>197.4563277395255</v>
+        <v>2443.987754662811</v>
       </c>
       <c r="I18">
-        <v>120.089059116205</v>
+        <v>572.502395078568</v>
       </c>
       <c r="J18">
-        <v>1.552194632860633</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>0.3059080276245129</v>
+      </c>
+      <c r="K18">
+        <v>0.3380359538615803</v>
+      </c>
+      <c r="L18">
+        <v>0.4082140634723086</v>
+      </c>
+      <c r="M18">
+        <v>1.270322451337524</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D19">
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F19" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G19">
-        <v>1871.485359674304</v>
+        <v>77.36726861959747</v>
       </c>
       <c r="H19">
-        <v>2443.987754662811</v>
+        <v>197.4563277395255</v>
       </c>
       <c r="I19">
-        <v>572.5023949885076</v>
+        <v>120.089059119928</v>
       </c>
       <c r="J19">
-        <v>0.3059080275616693</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>1.55219463298345</v>
+      </c>
+      <c r="K19">
+        <v>0.01397441786629883</v>
+      </c>
+      <c r="L19">
+        <v>0.03298070939639072</v>
+      </c>
+      <c r="M19">
+        <v>0.2664649602716653</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D20">
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F20" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G20">
-        <v>2723.489601760682</v>
+        <v>2723.489601629621</v>
       </c>
       <c r="H20">
         <v>2563.206669524415</v>
       </c>
       <c r="I20">
-        <v>-160.2829322362677</v>
+        <v>-160.2829321052063</v>
       </c>
       <c r="J20">
-        <v>-0.05885204486650066</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>-0.05885204482121018</v>
+      </c>
+      <c r="K20">
+        <v>0.4919287242105312</v>
+      </c>
+      <c r="L20">
+        <v>0.4281269446172998</v>
+      </c>
+      <c r="M20">
+        <v>-0.3556509264760523</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D21">
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F21" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G21">
-        <v>864.0077892081175</v>
+        <v>864.0077891665393</v>
       </c>
       <c r="H21">
         <v>782.3741287792515</v>
       </c>
       <c r="I21">
-        <v>-81.63366042886605</v>
+        <v>-81.63366038728782</v>
       </c>
       <c r="J21">
-        <v>-0.09448255148681603</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>-0.09448255144324025</v>
+      </c>
+      <c r="K21">
+        <v>0.1560609040615897</v>
+      </c>
+      <c r="L21">
+        <v>0.1306782825140009</v>
+      </c>
+      <c r="M21">
+        <v>-0.1811364851331371</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D22">
         <v>6</v>
       </c>
       <c r="E22" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F22" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G22">
-        <v>82.94024499744066</v>
+        <v>707.6201280218149</v>
       </c>
       <c r="H22">
-        <v>75.03353593469043</v>
+        <v>737.9275791029602</v>
       </c>
       <c r="I22">
-        <v>-7.906709062750224</v>
+        <v>30.30745108114525</v>
       </c>
       <c r="J22">
-        <v>-0.09533018696766819</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>0.04283011446532922</v>
+      </c>
+      <c r="K22">
+        <v>0.7214470007469835</v>
+      </c>
+      <c r="L22">
+        <v>0.7150284321689699</v>
+      </c>
+      <c r="M22">
+        <v>0.5920467287400174</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D23">
         <v>6</v>
       </c>
       <c r="E23" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F23" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G23">
-        <v>707.6201280068898</v>
+        <v>82.94024499919006</v>
       </c>
       <c r="H23">
-        <v>737.9275791029602</v>
+        <v>75.03353593469043</v>
       </c>
       <c r="I23">
-        <v>30.30745109607039</v>
+        <v>-7.906709064499623</v>
       </c>
       <c r="J23">
-        <v>0.04283011448732462</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>-0.09533018698674973</v>
+      </c>
+      <c r="K23">
+        <v>0.08456089450587388</v>
+      </c>
+      <c r="L23">
+        <v>0.072705117790414</v>
+      </c>
+      <c r="M23">
+        <v>-0.1544551280212495</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D24">
         <v>6</v>
       </c>
       <c r="E24" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F24" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G24">
-        <v>121.4343642338503</v>
+        <v>121.4343642364116</v>
       </c>
       <c r="H24">
         <v>137.9108006844309</v>
       </c>
       <c r="I24">
-        <v>16.47643645058055</v>
+        <v>16.47643644801924</v>
       </c>
       <c r="J24">
-        <v>0.1356818274179071</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>0.1356818273939532</v>
+      </c>
+      <c r="K24">
+        <v>0.1238071874960503</v>
+      </c>
+      <c r="L24">
+        <v>0.133631194151096</v>
+      </c>
+      <c r="M24">
+        <v>0.3218621148385261</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D25">
         <v>6</v>
       </c>
       <c r="E25" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F25" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G25">
-        <v>68.83979014113126</v>
+        <v>68.83979014258323</v>
       </c>
       <c r="H25">
         <v>81.15358970366472</v>
       </c>
       <c r="I25">
-        <v>12.31379956253346</v>
+        <v>12.3137995610815</v>
       </c>
       <c r="J25">
-        <v>0.1788761926392925</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>0.1788761926144277</v>
+      </c>
+      <c r="K25">
+        <v>0.07018491725109231</v>
+      </c>
+      <c r="L25">
+        <v>0.07863525588951994</v>
+      </c>
+      <c r="M25">
+        <v>0.240546284442706</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D26">
         <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G26">
-        <v>2778.358419243984</v>
+        <v>25481.64392898052</v>
       </c>
       <c r="H26">
-        <v>2795.482474226756</v>
+        <v>28420.73848797222</v>
       </c>
       <c r="I26">
-        <v>17.12405498277167</v>
+        <v>2939.094558991703</v>
       </c>
       <c r="J26">
-        <v>0.006163371458543235</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>0.1153416383645893</v>
+      </c>
+      <c r="K26">
+        <v>0.1457184745665642</v>
+      </c>
+      <c r="L26">
+        <v>0.1642038946162641</v>
+      </c>
+      <c r="M26">
+        <v>-1.644708762726218</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D27">
         <v>7</v>
       </c>
       <c r="E27" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F27" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G27">
-        <v>25481.64392898052</v>
+        <v>2778.358419243984</v>
       </c>
       <c r="H27">
-        <v>28420.73848797222</v>
+        <v>2795.482474226756</v>
       </c>
       <c r="I27">
-        <v>2939.094558991703</v>
+        <v>17.12405498277167</v>
       </c>
       <c r="J27">
-        <v>0.1153416383645893</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>0.006163371458543235</v>
+      </c>
+      <c r="K27">
+        <v>0.01588822729725671</v>
+      </c>
+      <c r="L27">
+        <v>0.01615120274914061</v>
+      </c>
+      <c r="M27">
+        <v>-0.009582571338988223</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D28">
         <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F28" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G28">
         <v>126740.1139747995</v>
@@ -3368,25 +4178,34 @@
       <c r="J28">
         <v>-0.03716554046055388</v>
       </c>
-    </row>
-    <row r="29" spans="1:10">
+      <c r="K28">
+        <v>0.7247717661495151</v>
+      </c>
+      <c r="L28">
+        <v>0.7050400916380323</v>
+      </c>
+      <c r="M28">
+        <v>2.635906454340069</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D29">
         <v>7</v>
       </c>
       <c r="E29" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F29" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G29">
         <v>19868.88367697594</v>
@@ -3400,217 +4219,280 @@
       <c r="J29">
         <v>-0.001653529237120245</v>
       </c>
-    </row>
-    <row r="30" spans="1:10">
+      <c r="K29">
+        <v>0.113621531986664</v>
+      </c>
+      <c r="L29">
+        <v>0.114604810996563</v>
+      </c>
+      <c r="M29">
+        <v>0.01838487972513793</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D30">
         <v>8</v>
       </c>
       <c r="E30" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G30">
-        <v>245.1520291012133</v>
+        <v>16239.19907059248</v>
       </c>
       <c r="H30">
-        <v>822.964234104015</v>
+        <v>19646.96893063571</v>
       </c>
       <c r="I30">
-        <v>577.8122050028016</v>
+        <v>3407.769860043232</v>
       </c>
       <c r="J30">
-        <v>2.356954609436443</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>0.2098483949380455</v>
+      </c>
+      <c r="K30">
+        <v>0.1538580630692243</v>
+      </c>
+      <c r="L30">
+        <v>0.1703395953757214</v>
+      </c>
+      <c r="M30">
+        <v>0.3479668013212717</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D31">
         <v>8</v>
       </c>
       <c r="E31" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F31" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G31">
-        <v>16239.19907449228</v>
+        <v>245.15202893786</v>
       </c>
       <c r="H31">
-        <v>19646.96893063571</v>
+        <v>822.964234104015</v>
       </c>
       <c r="I31">
-        <v>3407.76985614343</v>
+        <v>577.812205166155</v>
       </c>
       <c r="J31">
-        <v>0.2098483946475035</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+        <v>2.356954611673299</v>
+      </c>
+      <c r="K31">
+        <v>0.002322689448285298</v>
+      </c>
+      <c r="L31">
+        <v>0.007135115606936144</v>
+      </c>
+      <c r="M31">
+        <v>0.05900030608097068</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D32">
         <v>8</v>
       </c>
       <c r="E32" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F32" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G32">
-        <v>29614.11485274678</v>
+        <v>29614.11484696532</v>
       </c>
       <c r="H32">
         <v>29126.68352601153</v>
       </c>
       <c r="I32">
-        <v>-487.4313267352518</v>
+        <v>-487.4313209537868</v>
       </c>
       <c r="J32">
-        <v>-0.01645942582308994</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
+        <v>-0.01645942563107659</v>
+      </c>
+      <c r="K32">
+        <v>0.2805785143748106</v>
+      </c>
+      <c r="L32">
+        <v>0.2525289017341038</v>
+      </c>
+      <c r="M32">
+        <v>-0.04977152935261291</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D33">
         <v>8</v>
       </c>
       <c r="E33" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F33" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G33">
-        <v>59448.15766655401</v>
+        <v>59448.15765350434</v>
       </c>
       <c r="H33">
         <v>65743.38330924875</v>
       </c>
       <c r="I33">
-        <v>6295.225642694742</v>
+        <v>6295.225655744405</v>
       </c>
       <c r="J33">
-        <v>0.1058943773834809</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
+        <v>0.1058943776262394</v>
+      </c>
+      <c r="K33">
+        <v>0.5632407331076799</v>
+      </c>
+      <c r="L33">
+        <v>0.5699963872832385</v>
+      </c>
+      <c r="M33">
+        <v>0.6428044219503707</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D34">
         <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F34" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G34">
-        <v>1.266579215857656</v>
+        <v>4753.509400961959</v>
       </c>
       <c r="H34">
-        <v>50.72146917358625</v>
+        <v>6147.44206383908</v>
       </c>
       <c r="I34">
-        <v>49.4548899577286</v>
+        <v>1393.932662877121</v>
       </c>
       <c r="J34">
-        <v>39.04602991944765</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+        <v>0.2932428539207336</v>
+      </c>
+      <c r="K34">
+        <v>0.07180744736943652</v>
+      </c>
+      <c r="L34">
+        <v>0.08832531700918218</v>
+      </c>
+      <c r="M34">
+        <v>0.4097391719215528</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D35">
         <v>9</v>
       </c>
       <c r="E35" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F35" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G35">
-        <v>4753.509400961959</v>
+        <v>1.266579215857656</v>
       </c>
       <c r="H35">
-        <v>6147.44206383908</v>
+        <v>50.72146917358625</v>
       </c>
       <c r="I35">
-        <v>1393.932662877121</v>
+        <v>49.4548899577286</v>
       </c>
       <c r="J35">
-        <v>0.2932428539207336</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+        <v>39.04602991944765</v>
+      </c>
+      <c r="K35">
+        <v>1.913319459587384E-05</v>
+      </c>
+      <c r="L35">
+        <v>0.0007287567409998024</v>
+      </c>
+      <c r="M35">
+        <v>0.01453700469069037</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C36" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D36">
         <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F36" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G36">
         <v>10848.79201282612</v>
@@ -3624,25 +4506,34 @@
       <c r="J36">
         <v>0.1398406541393198</v>
       </c>
-    </row>
-    <row r="37" spans="1:10">
+      <c r="K36">
+        <v>0.163883984604159</v>
+      </c>
+      <c r="L36">
+        <v>0.1776708934557636</v>
+      </c>
+      <c r="M36">
+        <v>0.4459442009685579</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D37">
         <v>9</v>
       </c>
       <c r="E37" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F37" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G37">
         <v>50594.43200699607</v>
@@ -3656,89 +4547,116 @@
       <c r="J37">
         <v>0.008726459769507124</v>
       </c>
-    </row>
-    <row r="38" spans="1:10">
+      <c r="K37">
+        <v>0.7642894348318087</v>
+      </c>
+      <c r="L37">
+        <v>0.7332750327940544</v>
+      </c>
+      <c r="M37">
+        <v>0.129779622419199</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D38">
         <v>10</v>
       </c>
       <c r="E38" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F38" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G38">
-        <v>4.706132879045919</v>
+        <v>1791.908006814309</v>
       </c>
       <c r="H38">
-        <v>129.8034497444613</v>
+        <v>3914.073253833027</v>
       </c>
       <c r="I38">
-        <v>125.0973168654153</v>
+        <v>2122.165247018718</v>
       </c>
       <c r="J38">
-        <v>26.58176470588236</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
+        <v>1.184304796311249</v>
+      </c>
+      <c r="K38">
+        <v>0.03831319236293157</v>
+      </c>
+      <c r="L38">
+        <v>0.08347529812606425</v>
+      </c>
+      <c r="M38">
+        <v>17.83332140351762</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C39" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D39">
         <v>10</v>
       </c>
       <c r="E39" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F39" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G39">
-        <v>1791.908006814309</v>
+        <v>4.706132879045919</v>
       </c>
       <c r="H39">
-        <v>3914.073253833027</v>
+        <v>129.8034497444613</v>
       </c>
       <c r="I39">
-        <v>2122.165247018718</v>
+        <v>125.0973168654153</v>
       </c>
       <c r="J39">
-        <v>1.184304796311249</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
+        <v>26.58176470588236</v>
+      </c>
+      <c r="K39">
+        <v>0.0001006228967082728</v>
+      </c>
+      <c r="L39">
+        <v>0.002768313458262305</v>
+      </c>
+      <c r="M39">
+        <v>1.051237956852169</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C40" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D40">
         <v>10</v>
       </c>
       <c r="E40" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F40" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G40">
         <v>5201.051959114139</v>
@@ -3752,25 +4670,34 @@
       <c r="J40">
         <v>0.1192323250685572</v>
       </c>
-    </row>
-    <row r="41" spans="1:10">
+      <c r="K40">
+        <v>0.1112048740456305</v>
+      </c>
+      <c r="L40">
+        <v>0.1241482112436113</v>
+      </c>
+      <c r="M40">
+        <v>5.211206032668217</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C41" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D41">
         <v>10</v>
       </c>
       <c r="E41" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F41" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G41">
         <v>39772.33390119251</v>
@@ -3783,6 +4710,15 @@
       </c>
       <c r="J41">
         <v>-0.06910321352022225</v>
+      </c>
+      <c r="K41">
+        <v>0.8503813106947297</v>
+      </c>
+      <c r="L41">
+        <v>0.7896081771720621</v>
+      </c>
+      <c r="M41">
+        <v>-23.095765393038</v>
       </c>
     </row>
   </sheetData>
